--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -26,6 +26,7 @@
     <sheet name="2026-02-11" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-02-18" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16876,6 +16877,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>暁のヨナ</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ふたりソロキャンプ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>青のオーケストラ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>天国大魔境</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>きのう何食べた?</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>直径3cmの召喚陣&lt;リミットリング&gt;で「雑魚すら呼べない」と蔑まれた底辺召喚士が頂点に立つまで1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>チカーノKEI~米国極悪刑務所を生き抜いた日本人~</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>四天王最弱だった俺。転生したので平穏な生活を望む コミック版</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>勇者パーティを追放された、仲間のスキルを解放して最強に成り上がる2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>私刑執行人~殺人弁護士とテミスの天秤~</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>異世界好色無双録 ~異世界転生の知恵と力を、ただひたすら××××するために使う~</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>最強ギルドを追放された《植物王》、実は世界樹に選ばれていたので植物の力で無双します1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>放課後ていぼう日誌</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GANTZ:E</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>拝啓、役立たず令嬢から親愛なる騎士様へ~地味な魔法でも貴方の役に立ってみせます1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>テンカイチ 日本最強武芸者決定戦</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>出禁のモグラ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>バブル~チカーノKEI歌舞伎町血闘編~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>パラショッパーズ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ハネチンとブッキーのお子さま診療録</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>むせるくらいの愛をあげる</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>悪女に仕立て上げられた薄幸令嬢の幸せな婚約破棄1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>出来損ない皇子の成り上がり~聖痕無しの第三皇子に転生したけど、今度こそ家族を守るために最強を目指す~1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ヒミコ先生の狂育指導</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>大自然の魔法師アシュト、廃れた領地でスローライフ7</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>追放された転生貴族、外れスキルで内政無双~気ままに領地運営するはずが、スキル『ガチャ』のお陰で最強領地を作り上げてしまった~</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>高校時代に傲慢だった女王様との同棲生活は意外と居心地が悪くない</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>マリッジシンデレラ 拾われた花嫁は一途な副社長に溺愛される</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>青のミブロー新選組編ー</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>多聞くん今どっち!?</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>超辺境の領主アローの生活 ~濡れ衣を着せられ追放されましたが、二人の女神と新生活を送ります~ コミック版</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ニセモノの錬金術師</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>無職転生 ~異世界行ったら本気だす~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>もふもふと異世界でスローライフを目指します!16</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>聖なる乙女と秘めごとを</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>聖者無双</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>紛争でしたら八田まで</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>釣って食べたいギャル澤さん</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>水属性の魔法使い@COMIC</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>とある魔術の禁書目録</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>かつて買われた私たち第1話</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>婚約破棄された男爵令嬢リルジェシカは得意の靴作りで借金返済中!1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>退学の末に勘当された騎士は、超絶スキル「絆召喚術」を会得し最強となる コミック版</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>細菌少女</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>後宮の生贄妃~どうせ死ぬのなら、皇帝に愛されます~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>だんドーン</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>寝取り魔法使いの冒険</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>血を這う亡国の王女</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ギルド追放された雑用係の下剋上~超万能な生活スキルで世界最強~</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>シルバーマウンテン</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>離婚予定の契約婚なのに、冷酷公爵様に執着されています</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>タケトのゾゾッとCOMIC 配信後に消したヤバい話</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>元貧乏エルフの錬金術調薬店 第3話</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>もういい加減にして...~「理想の夫」は自己中クズ男~</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>最凶貴族は死亡フラグを覆す1</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>再愛~次期社長ともう一度~</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>志乃と恋</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>バクガタリzzZ</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ぐがぐもぐるてん</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ストーンフラワー</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>性癖退散!</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ヒミコ先生の狂育指導</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>洗脳されかけていた悪役令嬢ですが家出を決意しました。1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>魔法少女にあこがれて</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>「くじ」から始まる婚約生活~厳正なる抽選の結果、笑わない次期公爵様の婚約者に当選しました~</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>落ちこぼれ魔法使いは、今日も無意識にチートを使う7</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>定額制夫の「こづかい万歳」 月額2万千円の金欠ライフ</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ヤンキー君と科学ごはん</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>100万の命の上に俺は立っている</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>戦隊大失格</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -27,6 +27,7 @@
     <sheet name="2026-02-18" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18213,6 +18214,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>お気楽領主の楽しい領地防衛</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>路傍のフジイ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>異世界クラフトぐらし~自由気ままな生産職のほのぼのスローライフ~(コミック)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>妹の召使いから解放された私は公爵家の家庭教師になりまして コミック版</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>暁のヨナ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Re:blue</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>汚名を着せられ婚約破棄された伯爵令嬢は、結婚に理想は抱かない コミック版</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ふたりソロキャンプ</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHIORI EXPERIENCE ジミなわたしとヘンなおじさん</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ギャラリーフェイク</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>日に流れて橋に行く</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8歳から始める魔法学</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>異世界で 上前はねて 生きていく~再生魔法使いのゆるふわ人材派遣生活~(コミック)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>賢者の弟子を名乗る賢者 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>オーイ! とんぼ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>虎王の花嫁さん</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>不可抗力のI LOVE YOU</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>きのう何食べた?</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>最強ギルドを追放された《植物王》、実は世界樹に選ばれていたので植物の力で無双します1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>捨てられた妃 めでたく離縁が成立したので出ていったら、竜国の王太子からの溺愛が待っていました</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>聖女と皇王の誓約結婚 恥ずかしいので聖女の自慢話はしないでくださいね…!</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZOMBIE vs 鬼娘</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>いびってこない義母と義姉:</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>家政魔導士の異世界生活~冒険中の家政婦業承ります!~:</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>異世界で土地を買って農場を作ろう</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>真の聖女である私は追放されました。だからこの国はもう終わりです</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>青のオーケストラ</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>紫雲寺家の子供たち</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>闇金ウシジマくん外伝 肉蝮伝説</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ステータス・オール∞(インフィニティ) ∞使いの最強能力者、異世界を自由気ままに暮らします!</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>星降る王国のニナ</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ハーレム・アップライジング ~女尊男卑の世界で魔王の力を使って支配します~</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>勇者パーティを追放された、仲間のスキルを解放して最強に成り上がる2</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>直径3cmの召喚陣&lt;リミットリング&gt;で「雑魚すら呼べない」と蔑まれた底辺召喚士が頂点に立つまで1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>美形王子が苦手な破天荒モブ令嬢は自分らしく生きていきたい! コミック版</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>黒騎士様から全力で溺愛されていますが、すごもり聖女は今日も引きこもりたい!</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ゾンビのあふれた世界で俺だけが襲われない 時子 IF STORY(フルカラー) 第2話 生存者たち</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>お兄ちゃんのおさがり彼女1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>私以外みんな幸せ</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>家を追放された魔法薬師は、薬獣や妖精に囲まれて秘密の薬草園で第二の人生を謳歌する</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>最後の陰陽師とその妻</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>聖女と皇王の誓約結婚 恥ずかしいので聖女の自慢話はしないでくださいね…!</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>聖女と皇王の誓約結婚 恥ずかしいので聖女の自慢話はしないでくださいね…!</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>お気楽領主の楽しい領地防衛</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>「お前ごときが魔王に勝てると思うな」と勇者パーティを追放されたので、王都で気ままに暮らしたい THE COMIC</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>悪役令嬢の兄に転生しました</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>玉川さん 出てました?</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>お気楽領主の楽しい領地防衛</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>黄昏流星群</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>君を忘れる恋がしたい</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>呪術廻戦</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ぬめり</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>不謹慎電脳アンダーグラウンド</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ちょいクズ社畜の異世界ハーレム建国記</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>四天王最弱だった俺。転生したので平穏な生活を望む コミック版</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>人妻教師が教え子の女子高生にドはまりする話</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Berry’sFantasyならば、悪女になりましょう~亡き者にした令嬢からやり返される気分はいかがですか?~</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>獣人皇帝は男装令嬢を溺愛する ただの従者のはずですが! コミック版</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>呪われ彼ピを祓いたい1</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>無能は不要と言われ『時計使い』の僕は職人ギルドから追い出されるも、ダンジョンの深部で真の力に覚醒する THE COMIC</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>30分の金魚鉢</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>飲んで、滑って、奈落まで。</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>最後の陰陽師とその妻</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>最後の陰陽師とその妻</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>悪役令嬢後宮物語 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ZOMBIE vs 鬼娘</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>学園のマドンナの渡辺さんが、なぜか毎週予定を聞いてくる@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>撲殺ピンク~性犯罪者処刑人~</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>おっさんのリメイク冒険日記  ~オートキャンプから始まる異世界満喫ライフ~</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>無職転生 ~異世界行ったら本気だす~</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>天国大魔境</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>出禁のモグラ</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>継母の心得3</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>チカーノKEI~米国極悪刑務所を生き抜いた日本人~</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>お気楽領主の楽しい領地防衛</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>不器用な先輩。</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>黒の召喚士</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ありす、宇宙までも</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>うっちゃれ五所瓦 粘り腰編</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>キッチンカー『デリ・ジョイ』―車窓から異世界へ美味いもの密輸販売中!―</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>王様ランキング</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GANTZ:E</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>バツイチがモテるなんて聞いてません</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>剣に焦ぐ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>はじめの一歩</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ガチアクタ</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>29歳独身中堅冒険者の日常</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -28,6 +28,7 @@
     <sheet name="2026-02-25" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19550,6 +19551,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1日外出録ハンチョウ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放されたビーストテイマー、最強種の猫耳少女と出会う</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>異世界賢者の転生無双 ~ゲームの知識で異世界最強~</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>あなたのお城の小人さん ~御飯下さい、働きますっ~(コミック) 通常版</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ルリドラゴン</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中華一番!極</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>異世界転移したのでチートを生かして魔法剣士やることにする</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>天堂家物語</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ひまてん!</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>バキ外伝 烈海王は異世界転生しても一向にかまわんッッ</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>彼岸島 48日後…</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>魔導具師ダリヤはうつむかない ~Dahliya Wilts No More~</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>実は俺、最強でした?</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>技巧貸与&lt;スキル・レンダー&gt;のとりかえし~トイチって最初に言ったよな?~</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>昴と彗星</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>サンキューピッチ</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>葬送のフリーレン</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ゴールデンドロップ</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>平成敗残兵すみれちゃん</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥~生まれ変わって今更やり直す2度目の学院生活~</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>路傍のフジイ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>きみは四葉のクローバー</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ウォルテニア戦記12</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>そうだ、売国しよう~天才王子の赤字国家再生術~</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>底辺戦士、チート魔導師に転職する!</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ふつうの軽音部</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ティアムーン帝国物語~断頭台から始まる、姫の転生逆転ストーリー~@COMIC</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>悪女に仕立て上げられた薄幸令嬢の幸せな婚約破棄1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>クラスで2番目に可愛いボーイッシュ幼馴染の完全攻略神託チャート</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Aランクパーティを離脱した俺は、元教え子たちと迷宮深部を目指す。</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SHIORI EXPERIENCE ジミなわたしとヘンなおじさん</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>魔剣の弟子は無能で最強!~英雄流の修行で万能になれたので、最強を目指します~(コミック)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>魔物喰らいの冒険者</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ラブファントム</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>しのびごと</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>かくして魔法使いノイ・ガレネーは100年後、花嫁となった</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>かくして魔法使いノイ・ガレネーは100年後、花嫁となった</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>かくして魔法使いノイ・ガレネーは100年後、花嫁となった</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>クラスで2番目に可愛いボーイッシュ幼馴染の完全攻略神託チャート</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>クラスで2番目に可愛いボーイッシュ幼馴染の完全攻略神託チャート</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>推しの執着心を舐めていた</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>推しの執着心を舐めていた</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>推しの執着心を舐めていた</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>WORST外伝 ドクロ</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>異世界のんびり農家</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>今夜もシリアルキラーと待ち合わせ</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>伍と碁</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>チカーノKEI~米国極悪刑務所を生き抜いた日本人~</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ゴーストフィクサーズ</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>隣国から来た嫁が可愛すぎてどうしよう。(コミック)3</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ダンジョンに閉じ込められて25年。救出されたときには立派な不審者になっていた</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ありす、宇宙までも</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ポンコツ風紀委員とスカート丈が不適切なJKの話</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>天傍台閣</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>今どきの若いモンは</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ヤンキーJKクズハナちゃん</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>結婚しましょう、恋する前に</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>猫に白鳥、蛍に小判</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>上手いって言え!!!!!!</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>旦那様、稼いで離婚させていただきます!</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>旦那様、稼いで離婚させていただきます!</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>旦那様、稼いで離婚させていただきます!</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>路地裏で拾った女の子がバッドエンド後の乙女ゲームのヒロインだった件</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>怪獣自衛隊</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>WORST外伝 グリコ</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>黄金の経験値</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>賢者の弟子を名乗る賢者 THE COMIC</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>義妹に婚約者を奪われた落ちこぼれ令嬢は、天才魔術師に溺愛される(コミック)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -29,6 +29,7 @@
     <sheet name="2026-03-04" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20887,6 +20888,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>わたしの幸せな結婚 通常版</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>出会って5秒でバトル</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>運命の人に出会う話</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>なのに、千輝くんが甘すぎる。</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>不徳のギルド</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1日外出録ハンチョウ</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>やんごとなき一族</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>どうせ、恋してしまうんだ。</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ラブファントム</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ブラックパーティーを追放されたボクは、『肉食系』な聖女様と背徳的な行為をしています。1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔導具師ダリヤはうつむかない ~Dahliya Wilts No More~</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>魔女と傭兵</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>異世界でも無難に生きたい症候群</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ながたんと青と-いちかの料理帖-</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>結婚しましょう、恋する前に</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>緑の歌姫</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>僕の彼女が重すぎる</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>桃の園</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>酒と恋には酔って然るべき</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ファミレス行こ。 下</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>私たちはどうかしている 妻恋い</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>いずれ最強の錬金術師?9</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>サイコアイズ</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放されたビーストテイマー、最強種の猫耳少女と出会う</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>君は冥土様。</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>絶対魅了で異世界攻略!~高慢女わからせハーレム計画~</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>グッバイ・モーニング</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ヘヴンシステム上巻</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>実は俺、最強でした?</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Aランクパーティを離脱した俺は、元教え子たちと迷宮深部を目指す。</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放された俺だが、俺から巣立ってくれたようで嬉しい。……なので大聖女、お前に追って来られては困るのだが?(コミック)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ごほうびは、バイトのあとで~雨宮くんちで家事代行はじめました~</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>もう逃がさないから、覚悟して</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>逆さのクラゲはあなたの顔</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>邪神監禁ハーレムで異世界征服</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>公爵令嬢の地味な付き人~魔神封印に貢献しすぎたので、実力を隠します~1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ゆいっこ</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>彼岸島 48日後…</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>白衣の英雄(コミック)</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>転生したら序盤で死ぬ中ボスだった-ヒロイン眷属化で生き残る-</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ティアムーン帝国物語~断頭台から始まる、姫の転生逆転ストーリー~@COMIC</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>没落予定の貴族だけど、暇だったから魔法を極めてみた@COMIC</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>理系が恋に落ちたので証明してみた。</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>憂国のモリアーティ</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>葬送のフリーレン</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ルリドラゴン</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>社長が私を抱く理由</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>大嫌いな運命の人1</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>溺愛したりない。</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>この恋は甘くない、はずでした</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>絶対魅了で異世界攻略!~高慢女わからせハーレム計画~</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>絶対魅了で異世界攻略!~高慢女わからせハーレム計画~</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>邪神監禁ハーレムで異世界征服</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>邪神監禁ハーレムで異世界征服</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>爆乳エルフに搾り取られて、今日も僕は勇者になれない。</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>萌音ちゃんの反省会通話</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>太らせJKこはねちゃん</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>レベルアップデイズ~幼馴染の攻略サポート~</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Summons Lord~元伝説の勇者なボク、召喚スキルでお姉さんモンスターたちとハーレムを築いちゃいます!?~</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>オフサイド</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>オフサイド</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>愛され聖女は闇堕ち悪役を救いたい</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>敵国で冷遇された皇女様は夫の愛に気づかない</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>転生貴族の異世界冒険録~カインのやりすぎギルド日記~(ポルカコミックス)10</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>昔勇者で今は骨</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>転生しまして、現在は侍女でございます。 10(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>うちの会社の小さい先輩の話</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>不死王はスローライフを希望します6</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ハズレ判定から始まったチート魔術士生活(コミック)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>天国大魔境</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>魔物喰らいの冒険者</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ひねくれ騎士とふわふわ姫様 古城暮らしと小さなおうち</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>家から逃げ出したい私が、うっかり憧れの大魔法使い様を買ってしまったら(コミック)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -30,6 +30,7 @@
     <sheet name="2026-03-11" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22224,6 +22225,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ウマ娘 シンデレラグレイ</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>序盤で死ぬ最強のサブキャラに転生したので、ゲーム知識で無双する1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ジャンケットバンク</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>オタクに優しいギャルはいない!?</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>帝乃三姉妹は案外、チョロい。</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>グラゼニ~大リーグ編~</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>終末のワルキューレ禁伝 神々の黙示録</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>春の嵐とモンスター</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KING GOLF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>解雇された暗黒兵士のスローなセカンドライフ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>魔女大戦 32人の異才の魔女は殺し合う</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>黒岩メダカに私の可愛いが通じない</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DEAR BOYS ACT4</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>わたしの幸せな結婚 通常版</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>史上最強の魔法剣士、Fランク冒険者に転生する ~剣聖と魔帝、2つの前世を持った男の英雄譚~</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>訳あり幼女、転生したことに気づいたのは、修羅場に遭遇した時。1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>転生ゴブリンだけど質問ある?</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>盤上のオリオン</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>レッドブルー</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>究極難度の異世界に転移したのでゲーム知識を使って英雄になる1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>酒と恋には酔って然るべき</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>終末のワルキューレ奇譚 ジャック・ザ・リッパーの事件簿</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>転生貴族の万能開拓~スキルを使っていたら最強領地になりました~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>出会って5秒でバトル</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>塩対応の佐藤さんが俺にだけ甘い@comic</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>百瀬アキラの初恋破綻中。</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>顔だけじゃ好きになりません</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ブラックパーティーを追放されたボクは、『肉食系』な聖女様と背徳的な行為をしています。1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>異世界転生騒動記14</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ダンジョンに出会いを求めるのは間違っているだろうか 外伝 ソード・オラトリア</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>怨み屋本舗DIABLO</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>銀河英雄伝説</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>多聞くん今どっち!?</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>公爵令嬢の地味な付き人~魔神封印に貢献しすぎたので、実力を隠します~1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>15歳、今日から同棲はじめます。1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>いずれ最強の錬金術師?9</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>前田慶次 かぶき旅</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>焼いてるふたり</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>君のことが大大大大大好きな100人の彼女</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>みずぽろ</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>社畜テイマー、可愛いスライムのおかげで無自覚なまま無双する~うっかり国内トップの配信に映り込んで最強がバレました~</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>尾守つみきと奇日常。</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>離婚予定の契約婚なのに、冷酷公爵様に執着されています</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ぼんたん激動編 姫武将まさむね参る!!  序</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>俺の許嫁になった地味子、家では可愛いしかない。</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>東京決闘環状戦</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>雪と墨</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>十字架のろくにん</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>魔導具師ダリヤはうつむかない ~Dahliya Wilts No More~</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>異世界でも無難に生きたい症候群</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>最強の職業は勇者でも賢者でもなく鑑定士(仮)らしいですよ?11</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>二階堂地獄ゴルフ</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>裏バイト:逃亡禁止</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放されたビーストテイマー、最強種の猫耳少女と出会う</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>路傍のフジイ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>転生格ゲーマー ~オジでも勝てる異世界攻略~</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ティアムーン帝国物語~断頭台から始まる、姫の転生逆転ストーリー~@COMIC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>運命の人に出会う話</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>中華一番!極</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>暁のヨナ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>これって、どこから恋ですか?</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>トニカクカワイイ</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>アーサー・ラザフォード氏の遅すぎる初恋 番外編</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ゆいっこ</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>やさぐれ召喚者は動かない(コミック) 1話</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>愛人マンションにて~平凡な私が芸能人に囲われた話~</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>クリスティ・ロンドンマッシブ</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>再愛~次期社長ともう一度~</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>彼の世に百合が咲くものか</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>直径3cmの召喚陣&lt;リミットリング&gt;で「雑魚すら呼べない」と蔑まれた底辺召喚士が頂点に立つまで1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>服飾師ルチアはあきらめない ~今日から始める幸服計画~</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -31,6 +31,7 @@
     <sheet name="2026-03-18" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23561,6 +23562,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>不運からの最強男</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>咲-Saki-</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lv2からチートだった元勇者候補のまったり異世界ライフ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ハズレ職〈召喚士〉がS級万能職に化けました~無能と蔑まれた俺、伝説の召喚獣達に懐かれ力が覚醒したので世界最強です~</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>隣の元カレくん 単行本版</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>序盤で死ぬ最強のサブキャラに転生したので、ゲーム知識で無双する1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>転生したら剣でした</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>グラゼニ~大リーグ編~</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>父は英雄、母は精霊、娘の私は転生者。</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>魔法が使えないモブキャラに転生したけど、俺だけ使えるで成り上がる~推しの悪役令嬢の兄となった男は破滅フラグを叩き斬り、ゲーム世界で無双する~</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>本なら売るほど</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ダンジョンに出会いを求めるのは間違っているだろうか 外伝 ソード・オラトリア</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>あなたの戸籍、俺にください。1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>離婚したはずなのに、冷徹エリート御曹司に容赦なく溺愛されています1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>悪女に奪われたヒロインの座、取り戻します!1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>義妹にすべてを奪われたのに元婚約者(上司)が溺愛してきます。1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>オタク君の性癖を一生歪めていく異種族娘たち</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>初恋ゴシップ1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>オルクセン王国史~野蛮なオークの国は、如何にして平和なエルフの国を焼き払うに至ったか~(ノヴァコミックス)6</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>モブから始まる探索英雄譚</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>オーバーロード &lt;新&gt;世界編</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>自称悪役令嬢な妻の観察記録。4</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>きみとバラ色の日々</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>めんとりさま</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ドキドキドキドキ</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>アメと傷</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>オタク君の性癖を一生歪めていく異種族娘たち</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>オタク君の性癖を一生歪めていく異種族娘たち</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>柳原くんはセックス依存症。1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ブリンブリン皇国物語~古の皇女と七人の護人~</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>転生した空間魔法使いは正体隠して目立ちたい!</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>私を喰べたい、ひとでなし</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>本なら売るほど</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0歳児スタートダッシュ物語IX</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ふつつかな悪女ではございますが ~雛宮蝶鼠とりかえ伝~:</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>二階堂地獄ゴルフ</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>メダリスト</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>文豪ストレイドッグス</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>わたしの幸せな結婚 通常版</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>雅血の陰陽師</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>没落貴族の俺がハズレ(?)スキル『超器用貧乏』で大賢者と呼ばれるまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>影の宮廷魔術師 9 ~無能だと思われていた男、実は最強の軍師だった~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>俺の前世の知識で底辺職テイマーが上級職になってしまいそうな件</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>絶対に働きたくないダンジョンマスターが惰眠をむさぼるまで</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>帝乃三姉妹は案外、チョロい。</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>愛でて春~呪われた公爵騎士様は溺愛する~</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ワールドトリガー</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~(話売り) #43</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>死神聖女</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>死神聖女</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>死神聖女</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>元英雄は大都会最強の便利屋さん1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ゴミ箱ぐらしの聖女様1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>究極難度の異世界に転移したのでゲーム知識を使って英雄になる1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>訳あり幼女、転生したことに気づいたのは、修羅場に遭遇した時。1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>めんとりさま</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>めんとりさま</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ドキドキドキドキ</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ドキドキドキドキ</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>アメと傷</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>アメと傷</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>悪女のレッテルを貼られた追放令嬢ですが、最恐陛下の溺愛に捕まりました</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>冷酷な狼皇帝の契約花嫁~「お前は家族じゃない」と捨てられた令嬢が、獣人国で愛されて幸せになるまで~</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>この1冊で追いつける!魔法科高校の劣等生</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>追放された付与魔法使いの成り上がり~勇者パーティを陰から支えていたと知らなかったので戻って来い?との美少女たちに囲まれて幸せなので戻りません~(ノヴァコミックス)5</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>勇者の母ですが、魔王軍の幹部になりました。</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>胚培養士(はいばいようし)ミズイロ~不妊治療のスペシャリスト~</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>一億年ボタンを連打した俺は、気付いたら最強になっていた ~落第剣士の学院無双~</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>やり直し令嬢は竜帝陛下を攻略中</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>家事代行のアルバイトを始めたら学園一の美少女の家族に気に入られちゃいました。</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>転生してあらゆるモノに好かれながら異世界で好きな事をして生きて行く</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ビジネス婚ー好きになったら離婚しますー7</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>手に入れた催眠アプリで夢のハーレム生活を送りたい</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>魔法使いの婚約者 ~Eternally Yours~:</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>虫かぶり姫:</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>捨てられ男爵令嬢は黒騎士様のお気に入り:</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>国を追われた竜師さん、拾われた隣国でうっかり無双してしまう。~弱小国家が大陸最強の竜の楽園になるまで~</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>焼いてるふたり</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>最強の職業は勇者でも賢者でもなく鑑定士(仮)らしいですよ?11</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ほっといて下さい 従魔とチートライフ楽しみたい!6</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>おい、外れスキルだと思われていた《チートコード操作》が化け物すぎるんだが。(コミック)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>シノハユ the dawn of age</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>綺麗にしてもらえますか。 ~ふたりぐらし~</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>妖怪学校の先生はじめました!</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -32,6 +32,7 @@
     <sheet name="2026-03-25" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24898,6 +24899,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ONE PIECE カラー版</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>少年院ウシジマくん</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>てんぷる</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>夏目友人帳</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>俺の死亡フラグが留まるところを知らない</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>キン肉マン</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>幼稚園WARS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ラーメン赤猫</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ケントゥリア</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>鵺の陰陽師</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>賭ケグルイ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>出会って5秒でバトル</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>序盤で死ぬ最強のサブキャラに転生したので、ゲーム知識で無双する1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ハズレ職〈召喚士〉がS級万能職に化けました~無能と蔑まれた俺、伝説の召喚獣達に懐かれ力が覚醒したので世界最強です~</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>不運からの最強男</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>本好きの下剋上 フェルディナンドの館にて 第1話</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>魔法が使えないモブキャラに転生したけど、俺だけ使えるで成り上がる~推しの悪役令嬢の兄となった男は破滅フラグを叩き斬り、ゲーム世界で無双する~</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>訳あり幼女、転生したことに気づいたのは、修羅場に遭遇した時。1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>どく・どく・もり・もり</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ふつつかな悪女ではございますが ~雛宮蝶鼠とりかえ伝~:</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>虫かぶり姫:</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>アルスラーン戦記</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>マリッジトキシン</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>葬送のフリーレン</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ジョジョの奇妙な冒険 ザ・ジョジョランズ</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第二部「本のためなら巫女になる! 」 第1話</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第四部「貴族院の図書館を救いたい!」 第1話</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>モブから始まる探索英雄譚</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>フラジャイル</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>わたしの幸せな結婚 通常版</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>断罪された悪役令嬢は、逆行して完璧な悪女を目指す@COMIC</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>スノウボールアース</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>魔術士オーフェンはぐれ旅 プレ編</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>魔術士オーフェン無謀編</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>203号室</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>拾った奴隷たちが旅立って早十年、なぜか俺が伝説になっていた@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第一部「本がないなら作ればいい!」第1話</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第三部「領地に本を広げよう!」 第1話</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>煙霧公爵と氷の花嫁 第1話</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>魔王様、溺愛しすぎです!@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>大至急、運命の恋探してます!</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>日給10万の結婚</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>不運からの最強男</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>私の彼が姉の夫になった理由2</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>私の彼が姉の夫になった理由1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>どく・どく・もり・もり</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>クズ人間、治療します。ー人格整形外科ー</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ファリスの結婚</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>反逆の勇者~スキルを使って腹黒王女のココロとカラダを掌握せよ~</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>超!!! 天才発明令嬢のパワフル領地改革6</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDOL×IDOL STORY!</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>序盤で死ぬ最強のサブキャラに転生したので、ゲーム知識で無双する3</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BUNGO-unreal-</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -33,6 +33,7 @@
     <sheet name="2026-04-01" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26235,6 +26236,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>名探偵コナン</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>時々ボソッとロシア語でデレる隣のアーリャさん</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>リィンカーネーションの花弁</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蟻の王</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>合コンに行ったら女がいなかった話</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>波うららかに、めおと日和</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>辺境の薬師、都でSランク冒険者となる~英雄村の少年がチート薬で無自覚無双~</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>異世界メイドの三ツ星グルメ 現代ごはん作ったら王宮で大バズリしました</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>青のオーケストラ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>異世界ウォーキング</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ダンス・ダンス・ダンスール</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BREAK BACK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ビジネス婚ー好きになったら離婚しますー2</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>魔法使いの嫁</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>てんぷる</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>異世界魔王と召喚少女の奴隷魔術</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>きみの横顔を見ていた</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>リーフェの祝福 ~無属性魔法しか使えない落ちこぼれとしてほっといてください~ 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ドローイング 最強漫画家はお絵描きスキルで異世界無双する!18</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>穏やか貴族の休暇のすすめ。@COMIC</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>異世界に転移したら山の中だった。反動で強さよりも快適さを選びました。8</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>虫かぶり姫:</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>この世界は不完全すぎる</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>最強で最速の無限レベルアップ ~スキルとでレベル上限の枷が外れた俺は無双する~</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>やわ男とカタ子</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>おかしな転生XIV 最強パティシエ異世界降臨</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ONE PIECE カラー版</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ババンババンバンバンパイア</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>全自動魔法のコスパ無双 「成長スピードが超遅い」と追放されたが、放置しても経験値が集まるみたいです コミック版</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>わたしの幸せな結婚 通常版</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>暗殺後宮~暗殺女官・花鈴はゆったり生きたい~</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>夏目友人帳</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>コールドゲーム</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>蟲蝕のアイリス ~蟲にカラダを作り変えられた追放冒険者♀の蟲毒無双~</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>自分しか知らない彼氏の一面</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>寝ても覚めても独占したい</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>忍者と極道</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>落ちこぼれだった兄が実は最強 ~史上最強の勇者は転生し、学園で無自覚に無双する~</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>転生した大聖女は、聖女であることをひた隠す A Tale of The Great Saint14</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>贅沢三昧したいのです! ~貧乏領地の魔法改革 悪役令嬢なんてなりません!~8</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ちはやふる plus きみがため</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>名探偵コナン 犯人の犯沢さん</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>戦乙女たちと築く元・底辺村人の最強ハーレム</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>自分しか知らない彼氏の一面</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>自分しか知らない彼氏の一面</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>最強! かわいい! あきらギャル</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>貞操逆転世界ならモテると思っていたら</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>マリッジランドリー</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>サーキット・スイッチャー</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ひとごとごと</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>百鬼夜行抄</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ふつつかな悪女ではございますが ~雛宮蝶鼠とりかえ伝~:</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ラーメン赤猫</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>アンダーニンジャ</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で“最強”なのがバレまくる。~老害どもにはいい加減愛想が尽きました~</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -34,6 +34,7 @@
     <sheet name="2026-04-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27572,6 +27573,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>リアル</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MAJOR 2nd(メジャーセカンド)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ゾン100~ゾンビになるまでにしたい100のこと~</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>THE BAND</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>追い出された万能職に新しい人生が始まりました11</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>本好きの下剋上~司書になるためには手段を選んでいられません~第四部「貴族院の図書館を救いたい!12」</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>カッコウの許嫁</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>本なら売るほど</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>青のオーケストラ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>一瞬で治療していたのに役立たずと追放された天才治癒師、闇ヒーラーとして楽しく生きる(コミック)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>超難関ダンジョンで10万年修行した結果、世界最強に ~最弱無能の下剋上~(コミック)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>青のミブロー新選組編ー</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>異世界クラス召喚されたらR1○のスキルを獲得したので、○りたい放題させてもらいます!</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>経験人数が見えるメガネ</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>辺境の老騎士 バルド・ローエン</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>俺は星間国家の悪徳領主!</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>神様のバレー</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FAIRY TAIL 100 YEARS QUEST</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ドMな彼女の育て方</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>侯爵令嬢リディアの美しき決断~裏切られたのでこちらから婚約破棄させていただきます~1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>私刑執行人~殺人弁護士とテミスの天秤~</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>たかが子爵嫡男に高貴な人たちがグイグイきて困る@COMIC</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>女子高生除霊師アカネ!</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>あなた達それでも先生ですかっ!</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>俺、勇者じゃないですから。~VR世界の頂点に君臨せし男。転生し、レベル1の無職からリスタートする~</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>てんぷる</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>地味なおじさん、実は英雄でした。~自覚がないまま無双してたら、姪のダンジョン配信で晒されてたようです~</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>名探偵コナン</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>覗いてみる?~ドルオタの俺に推しが過剰ファンサしてくる件~</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>経験人数が見えるメガネ</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>よわよわ先生</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>カナン様はあくまでチョロい</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>のあ先輩はともだち。</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ウマ娘 プリティーダービー スターブロッサム</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>救世主《メシア》~異世界を救った元勇者が魔物のあふれる現実世界を無双する~</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>姉のともだち</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>本好きの下剋上 ~司書になるためには手段を選んでいられません~ 第五部 「途絶えた知識を繋げよう!1」</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ONE PIECE カラー版</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ちはやふる plus きみがため</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>キルアオ</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>キルアオ</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>リーフェの祝福 ~無属性魔法しか使えない落ちこぼれとしてほっといてください~ 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>完璧令嬢クラリーシャの輝きは逆境なんかじゃ曇らない ~婚約破棄されても自力で幸せをつかめばよいのでは?~</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>捨てられ才女は家族とのんびり生きることにします</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>置き去りにされた花嫁は、辺境騎士の不器用な愛に気づかない1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>魔術の果てを求める大魔術師 ~魔道を極めた俺が三百年後の技術革新を期待して転生したら、哀しくなるほど退化していた……~ 第1話</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>じゃあ、君の代わりに殺そうか?</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>もしも徳川家康が総理大臣になったら―絶東のアルゴナウタイ―</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>捨てられ騎士の逆転記!~女神と始めた第二の人生は伝説級の英雄だった件~(ポルカコミックス)5</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ババンババンバンバンパイア</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GIANT KILLING</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -35,6 +35,7 @@
     <sheet name="2026-04-15" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-05-13" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28909,6 +28910,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>青の祓魔師</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>永年雇用は可能でしょうか</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新米オッサン冒険者、最強パーティに死ぬほど鍛えられて無敵になる。13</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>終わりのセラフ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ドンケツ第2章</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ひらやすみ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ドラゴンクエスト ダイの大冒険 勇者アバンと獄炎の魔王</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>左ききのエレン</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>暴食のベルセルク~俺だけレベルという概念を突破する~ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>魔王の俺が奴隷エルフを嫁にしたんだが、どう愛でればいい?15</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ひまてん!</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>青い竜の谷 DX版</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>シャングリラ・フロンティア ~クソゲーハンター、神ゲーに挑まんとす~</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>神々の加護で生産革命~異世界の片隅でまったりスローライフしてたら、なぜか多彩な人材が集まって最強国家ができてました~(コミック)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>税金で買った本</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>オーイ! とんぼ</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>転生したら没落貴族だったので、を極めて家族を救います1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>平和の国の島崎へ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>地味な剣聖はそれでも最強です(コミック)11</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ROPPEN-六篇-</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>悪祓士のキヨシくん</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>大正身代わり婚~金平糖は甘くほどけて~</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>本なら売るほど</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>マイペースと歩く</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>マイペースと歩く</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>妃教育から逃げたい私(コミック)8</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>さむわんへるつ</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>僕とロボコ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>けむりはからだ</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>鉄棺の花嫁</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>夜のあかり~深夜保育所物語~</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>リベンジクロス~復讐の輪舞曲~</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>確かに私は、お嫁さんが欲しいと言いました。 ~女装の王子様はお断り!~</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>軍神と偽りの花嫁</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>君となら、明日を歌えるの</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ハズレスキル『ガチャ』で追放された俺は、わがまま幼馴染を絶縁し覚醒する ~万能チートスキルをゲットして、目指せ楽々最強スローライフ!~(コミック)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>死に戻りの幸薄令嬢、今世では最恐ラスボスお義兄様に溺愛されてます</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>義姉の代わりに、余命一年と言われる侯爵子息様と婚約することになりました</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>次期公爵夫人の役割だけを求めてきた、氷の薔薇と謳われる旦那様が家庭内ストーカーと化した件</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>異世界でもふもふなでなでするためにがんばってます。(コミック)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>王妃様は離婚したい ~異世界から聖女様が来たので、もうお役御免ですわね?~</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>スキップとローファー</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>復讐が足りない</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>東郷家へ嫁いだ話</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -36,6 +36,7 @@
     <sheet name="2026-04-22" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-05-13" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-05-20" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31782,6 +31783,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>貴族転生 ~恵まれた生まれから最強の力を得る~</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>神達に拾われた男</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>世界最強の魔女、始めました ~私だけ『攻略サイト』を見れる世界で自由に生きます~</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>逃げ上手の若君</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>悪役令嬢転生おじさん</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>追放された転生王子、『自動製作』スキルで領地を爆速で開拓し最強の村を作ってしまう~最強クラフトスキルで始める、楽々領地開拓スローライフ~</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>追放されたお嬢様の『モンスターを食べるほど強くなる』スキルは、1食で1レベルアップする前代未聞の最強スキルでした。3日で人類最強になりましたわ~!</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>マイペースと歩く</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>おっさん冒険者ケインの善行</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>「攻略本」を駆使する最強の魔法使い ~&lt;命令させろ&gt;とは言わせない俺流魔王討伐最善ルート~</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>青の祓魔師</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>私の玉の輿計画! ~望まれない側室ですが、むしろ好都合です~ 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>最高難度迷宮でパーティに置き去りにされたSランク剣士、本当に迷いまくって誰も知らない最深部へ ~俺の勘だとたぶんこっちが出口だと思う~(コミック)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>訳アリ心霊マンション</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>完璧すぎて可愛げがないと婚約破棄された聖女は隣国に売られる</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>史上最強オークさんの楽しい異世界ハーレムづくり</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>イーブルガール/ジャスティスボーイ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ドンケツ第2章</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>パリピ孔明</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>異世界マンチキン ーHP1のままで最強最速ダンジョン攻略ー</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>私が聖女?いいえ、悪役令嬢です!~なので、全員破滅は阻止させていただきます~</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>異世界サイハテ温泉紀行</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>今日から僕は、彼女のXXを解消する。</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>バイト先のネットカフェが、なぜかクラスの美少女たちの溜まり場になった件。 第1話</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>東島丹三郎は仮面ライダーになりたい</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>雑用付与術師が自分の最強に気付くまで(コミック)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ニートだけどハロワにいったら異世界につれてかれた15</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>妃教育から逃げたい私(コミック)8</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>友達の妹が俺にだけウザい</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>灰宮先輩は怖くてかわいい</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>正直不動産</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DEAD ROCK</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>終わりのセラフ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ワールドトリガー</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>逆転エンゲージメント~悪名高い御曹司が私にだけ甘すぎる~</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>理想のヒモ生活</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>今日から僕は、彼女のXXを解消する。</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>今日から僕は、彼女のXXを解消する。</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>創る庭</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>なぜ逃げるんだい? 僕の召喚獣は可愛いよ</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>精魂貯蔵者(リビドータンカー)~異世界の幽霊は可愛かった~</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>英國紅茶奇譚</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ンザンビ ─消えた娘を捜しています─</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>婚約者に裏切られた錬金術師は、独立して『ざまぁ』します コミック版</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>新米オッサン冒険者、最強パーティに死ぬほど鍛えられて無敵になる。13</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>とんがり帽子のアトリエ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>みいちゃんと山田さん</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>平和の国の島崎へ</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ジュミドロ</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>恋獄島 極地恋愛7</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>貴族転生 ~外伝 14歳ノアの無双旅行~</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ROPPEN-六篇-</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TSUYOSHI 誰も勝てない、アイツには</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -37,6 +37,7 @@
     <sheet name="2026-04-29" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-05-13" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-05-20" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-05-27" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33119,6 +33120,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ゆびさきと恋々</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>転生貴族の異世界冒険録</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ベー革</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>私の玉の輿計画! ~望まれない側室ですが、むしろ好都合です~ 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>黒岩メダカに私の可愛いが通じない</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>貴族転生 ~恵まれた生まれから最強の力を得る~</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>正直不動産</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>黒崎さんの一途な愛がとまらない</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>虚構推理</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>戦隊大失格</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>私の彼が姉の夫になった理由1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>海が走るエンドロール</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>神達に拾われた男</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>メガネ、時々、ヤンキーくん</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>いっそあなたがトドメを刺して</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>シルバーマウンテン</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>私の彼が姉の夫になった理由2</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>すみっこ漫画家のトンデモ『裏』事件簿</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>眠れるケモノは愛を叫ぶ</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>パーティー追放された魔力0の捨て駒剣士、最強魔導師たちに拾われ魔法至上の世界を剣で成り上がる第1話始まりの終わり</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>君を守り愛し尽くす~冷血警視正の隠しきれない激情~</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>にぶんのいち夫婦</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>にぶんのいち夫婦</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>静かなるドン ― もうひとつの最終章 ―</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ダンジョンの中のひと</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>黒月のイェルクナハト</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Shrink~精神科医ヨワイ~</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>訳アリ心霊マンション</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>転生したら皇帝でした~生まれながらの皇帝はこの先生き残れるか~@COMIC</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>灰仭巫覡</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>蒼く染めろ</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>パラショッパーズ</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>廻天のアルバス</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>悪役令嬢後宮物語 ~王国激動編~ 2(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>恋愛レベル99の男、落とします1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>英國紅茶奇譚</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>このキスは事故なのに色無しの私がなぜか最強の魔法使いにとらわれてます</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>龍神と許嫁の赤い花印</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S級勇者は退職したい!(コミック) 第1話</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>嘘つき陛下が私に執着する理由</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>9番目のムサシ ゴースト アンド グレイ</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>中年魔術師の悠々自適なダンジョン攻略~スキルオーブを使ったら最強スキルを手に入れたので、好きに生きようと思います~@COMIC</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>生まれ変わった剣聖、剣士が冷遇される魔術至上主義の学園で無双する</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>僕の愛しいよなさん</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>このキスは事故なのに色無しの私がなぜか最強の魔法使いにとらわれてます</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>このキスは事故なのに色無しの私がなぜか最強の魔法使いにとらわれてます</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>転生しまして、現在は侍女でございます。 1(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>怠惰の魔女スピーシィ</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>パーティー追放された魔力0の捨て駒剣士、最強魔導師たちに拾われ魔法至上の世界を剣で成り上がる第2話夕霧の晴れるとき</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>お衣装係の推し事浪漫@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ケジメつけさせてもらいます。元ヤン弁護士 東矢斎</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>祖父母をたずねて家出兄弟二人旅@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>うちのご主人様は噛みませんよ!1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>万年ヒラ教師の支援魔術師、最強の賢者になる~不人気の支援魔術師は給料泥棒だと魔術大学をクビになったが、出世した元教え子たちのおかげで何も困らない件~ 第1話</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>百姓貴族</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>聖女じゃなかったので、王宮でのんびりご飯を作ることにしました</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>千のスキルを持つ男 異世界で召喚獣はじめました!(ポルカコミックス)12</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>リアル</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>万能女中コニー・ヴィレ4</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -38,6 +38,7 @@
     <sheet name="2026-05-13" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-05-20" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-05-27" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-06-03" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34456,6 +34457,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーピリオド</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ハニーレモンソーダ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ベー革</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>太陽よりも眩しい星</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>勇者パーティを追放された、仲間のスキルを解放して最強に成り上がる1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>最果てのパラディンXV</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>最凶の支援職である俺は世界最強クランを従える</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>異世界ゆるり紀行 ~子育てしながら冒険者します~12</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>君と宇宙を歩くために</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>錬金術師の辺境再生スローライフ~S級パーティーで孤立した少女をかばったら追放されたので、一緒に幸せに暮らします~2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>とんでもスキルのおかげで俺の異世界ライフはままならない(良い意味で)~スキルが示す「雨宿り」をしたら伝説のドラゴンが仲間になって、気づけば王国まで救ってた~</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>異世界二度目のおっさん、どう考えても高校生勇者より強い3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>虚構推理</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ちょいクズ社畜の異世界ハーレム建国記</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>不遇スキルの錬金術師、辺境を開拓する8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>今日から使える異世界恋愛マニュアル</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>平成敗残兵すみれちゃん</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>貴族転生 ~恵まれた生まれから最強の力を得る~</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ラグナクリムゾン</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ワンパンマン</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>おれは鉄兵</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>あした天気になあれ</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>嫌われ者の悪役令息に転生したのに、なぜか周りが放っておいてくれない3</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>だんドーン</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>勇者パーティを追放された、仲間のスキルを解放して最強に成り上がる3</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D級冒険者の俺、なぜか勇者パーティーに勧誘されたあげく、王女につきまとわれてる</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>神さま学校の落ちこぼれ</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>パラショッパーズ</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>廻天のアルバス</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>呪術廻戦≡(モジュロ)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>役目を果たした日陰の勇者は、辺境で自由に生きていきます</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>悪女が恋に落ちた時</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>凍牌 コールドガール</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Shrink~精神科医ヨワイ~</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>九条の大罪</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>正直不動産</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>転生貴族の異世界冒険録</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>杖と剣のウィストリア</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>終わりのセラフ</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -39,6 +39,7 @@
     <sheet name="2026-05-20" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-05-27" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-06-03" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-06-10" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35793,6 +35794,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ハニーレモンソーダ</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブルーピリオド</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>傷モノの花嫁</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>自称悪役令嬢な婚約者の観察記録。</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>おひとり様には慣れましたので。 婚約者放置中!:</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>竜騎士のお気に入り:</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>捨てられ王子が最前線で敵国の兵士を治療したら実は第七皇女だった件</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>追放公爵、ダンジョンを踏破する!</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>勇者殺しの元暗殺者。~無職のおっさんから始まるセカンドライフ~</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>君と宇宙を歩くために</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ハブられルーン使いの異世界冒険譚</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>無限の魔術師</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>僕はまだその“感情”を知らない</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ナラク様は田舎でチョロい</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>名無し</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>乙女ゲームの破滅フラグしかない悪役令嬢に転生してしまった…:</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>引きこもり令嬢は話のわかる聖獣番:</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ドラフトキング</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>太陽よりも眩しい星</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>社内探偵</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>コンプ厨、ファンタジー化した現代を行く。</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>捨てられ王子が最前線で敵国の兵士を治療したら実は第七皇女だった件</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>捨てられ王子が最前線で敵国の兵士を治療したら実は第七皇女だった件</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>超ビビりな配信者でも編集しちゃえば怖くない説 ~ラブマツと巡る都市伝説ぶっ壊しツアー~</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>悪女に奪われたヒロインの座、取り戻します!1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>東方智霊奇伝 反則探偵さとり サンサーラ編</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ちょいクズ社畜の異世界ハーレム建国記</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>勇者パーティを追放された、仲間のスキルを解放して最強に成り上がる1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>のんべんだらりな転生者~貧乏農家を満喫す~(コミック)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>土竜の唄</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>追放公爵、ダンジョンを踏破する!</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>追放公爵、ダンジョンを踏破する!</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>キラー通りのソムリエ探偵</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ハブられルーン使いの異世界冒険譚</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ハブられルーン使いの異世界冒険譚</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>無限の魔術師</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>無限の魔術師</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>受付嬢に告白したくてギルドに通いつめたら英雄になってた</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>幸せカナコの殺し屋生活</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>売れ残りの奴隷エルフを拾ったので、娘にすることにした</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1年A組のモンスター:</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>落ちこぼれ白魔導士セシルは対象外のはずでした:</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>悪役令嬢に転生した母は子育て改革をいたします ~結婚はうんざりなので王太子殿下は聖女様に差し上げますね~</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ハナバス 苔石花江のバスケ論</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ドッグスレッド</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>剣に焦ぐ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>虎王の花嫁さん</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>お姉ちゃんの翠くん</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>コンプ厨、ファンタジー化した現代を行く。</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>コンプ厨、ファンタジー化した現代を行く。</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>僕はまだその“感情”を知らない</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>僕はまだその“感情”を知らない</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ナラク様は田舎でチョロい</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ナラク様は田舎でチョロい</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>受付嬢に告白したくてギルドに通いつめたら英雄になってた</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>メメメの滅滅滅ッ!</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>とんでもスキルのおかげで俺の異世界ライフはままならない(良い意味で)~スキルが示す「雨宿り」をしたら伝説のドラゴンが仲間になって、気づけば王国まで救ってた~</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>処刑される当て馬王子、私が幸せにいたします!第1話</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>あの子が壊した私の推し活</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>やさぐれ執事Vtuberとネガティブポンコツ令嬢Vtuberの虚実混在な配信生活@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>最終兵器家族 第1話</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>終末ゾンビキャンプ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MUJINA INTO THE DEEP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>魔法科高校の劣等生 動乱の序章編6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>シーカーズ~迷宮最強のおじさん、神配信者となる~</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>運送屋のおっさんがなぜか副業で絶対無敵剣士を務めることに~さえない人生を送ってた俺が魔王討伐の切り札に?~</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>上伊那ぼたん、酔へる姿は百合の花</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ボクラノキセキ:</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>信じていた仲間達にダンジョン奥地で殺されかけたがギフト『無限ガチャ』でレベル9999の仲間達を手に入れて元パーティーメンバーと世界に復讐&amp;『ざまぁ!』します!</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>断罪される公爵令嬢、生まれ変わってラスボスの王妃様の子どもになります</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>貴族令嬢に生まれたからには念願のだらだらニート生活したい。2</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>千年の花嫁</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>偽りの悪女ですが末永く幸せになりましょう~お望みの”恋多き女”を演じているのに夫の様子がおかしい~</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>異世界料理道14</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ベー革</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>妖怪学校の先生はじめました! 通常版</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>最果てのパラディンXV</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>モブ子の恋</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>神達に拾われた男</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ごくりっ</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>超大国のイケメン王太子に嫁ぎたくない!!(合本版)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 完全版</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 完全版</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 完全版</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 完全版</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 完全版</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -40,6 +40,7 @@
     <sheet name="2026-05-27" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-06-03" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-06-10" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-06-17" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37130,6 +37131,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>この音とまれ!</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる ~弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた~</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>空挺ドラゴンズ</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sランクパーティから解雇された~『呪いのアイテム』しか作れませんが、その性能はアーティファクト級なり……!~</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>図書館の大魔術師</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ハズレ枠ので最強になった俺がすべてを蹂躙するまで</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>お隣の天使様にいつの間にか駄目人間にされていた件</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>くま クマ 熊 ベアー(コミック)14</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>新テニスの王子様</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>アラフォー賢者の異世界生活日記~気ままな異世界教師ライフ~</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>彼岸島 48日後…</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>黒妖の花嫁~忌み嫌われた私が冷酷大尉に愛されるまで~1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ブルーピリオド</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>え、社内システム全てワンオペしている私を解雇ですか?(コミック)5</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>鵺の陰陽師</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ふらいんぐうぃっち</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>万能「村づくり」チートでお手軽スローライフ ~村ですが何か?~(コミック)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>栽培チートで最強菜園~え、ただの家庭菜園ですけど?~</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>漫画 ゆうえんち -バキ外伝-</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>実は俺、最強でした?</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>偽りのフレイヤ</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>伍と碁</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>バーサス</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>異世界転生したのでマゾ奴隷になる</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>光が死んだ夏</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥~生まれ変わって今更やり直す2度目の学院生活~</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>極主夫道</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>異世界魔法は遅れてる!13</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>サンキューピッチ</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん if Episode of 魔フィア</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SAKAMOTO DAYS</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>捨てられ王子が最前線で敵国の兵士を治療したら実は第七皇女だった件</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>異世界転生したのでマゾ奴隷になる</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>異世界転生したのでマゾ奴隷になる</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>傷モノの花嫁</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ゴールデンドロップ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>冒険者ライセンスを剥奪されたおっさんだけど、愛娘ができたのでのんびり人生を謳歌する</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>悪役令嬢は溺愛ルートに入りました!?(コミック)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>しのびごと</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ちょいクズ社畜の異世界ハーレム建国記</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>異世界魔法少女ラジカル☆ハルナ</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ライバルアライバル</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>三重県津市西区平山町3-15-7</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>三重県津市西区平山町3-15-7</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>鉄鍋のジャン</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>社畜過ぎて仕事を辞めることにした天才宮廷魔術師~辺境の地でスローライフを夢見るが、不届き者を倒していたら『最果ての魔女』と呼ばれるようになる~ 第1話</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>エリザベート~神の手を持つ王女~</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>公爵夫人の50のお茶レシピ</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>アトム ザ・ビギニング</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>撲殺ピンク~性犯罪者処刑人~</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>念願の悪役令嬢の身体を手に入れたぞ!</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>暴力万歳</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ゴールデン・ガイ</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>転生賢者の異世界ライフ~第二の職業を得て、世界最強になりました~</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>お隣の天使様にいつの間にか駄目人間にされていた件 after the rain</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>万年2位だからと勘当された少年、無自覚に無双する</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>天傍台閣</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>東郷家へ嫁いだ話</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>暴君王の初恋</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>自称悪役令嬢な婚約者の観察記録。</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>今日から使える異世界恋愛マニュアル</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>喪女OLですが、なぜか理想の筋肉に包囲されています。</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>気弱令嬢に成り代わった元悪女</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>黒妖の花嫁~忌み嫌われた私が冷酷大尉に愛されるまで~4</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>黒妖の花嫁~忌み嫌われた私が冷酷大尉に愛されるまで~5</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>猫降臨</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>恋するふたりは牙を隠す~ギャップがありすぎるカップルの話~</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ないものねだりの君に光の花束を</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>置き去りにされた花嫁は、辺境騎士の不器用な愛に気づかない1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>悪女に仕立て上げられた薄幸令嬢の幸せな婚約破棄1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>離婚したはずなのに、冷徹エリート御曹司に容赦なく溺愛されています1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>恋愛レベル99の男、落とします2</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>復讐声明</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>復讐声明</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>転生悪女皇帝ですが原作改変したら溺愛人生始まりました</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>うらはらマリッジ</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>束縛令嬢は海賊船長に奪われ自由になる</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>吸血公爵の愛が深すぎる(フルカラー)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>龍が娶るは災禍の娘</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -41,6 +41,7 @@
     <sheet name="2026-06-03" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-06-10" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-06-17" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026-06-24" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38467,6 +38468,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる ~弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>勇者パーティを追い出された器用貧乏 ~パーティ事情で付与術士をやっていた剣士、万能へと至る~</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>月が導く異世界道中17</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>恋ヶ窪くんにはじめてを奪われました</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ひかえめに言っても、これは愛</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金田一パパの事件簿</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WIND BREAKER</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>七つ屋志のぶの宝石匣</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>恋せよまやかし天使ども</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>図書館の大魔術師</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ハズレ枠ので最強になった俺がすべてを蹂躙するまで</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>空挺ドラゴンズ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>実は俺、最強でした?</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>魔術ギルド総帥~生まれ変わって今更やり直す2度目の学院生活~</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>異世界の貧乏農家に転生したので、レンガを作って城を建てることにしました@COMIC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ふらいんぐうぃっち</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>バーサス</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>王様ランキング</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>異世界転生の冒険者</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>極主夫道</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>火の神さまの掃除人ですが、いつの間にか花嫁として溺愛されています</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>マロニエ王国の七人の騎士</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>二度追放された冒険者、激レアスキル駆使して美少女軍団を育成中! コミック版</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>転生少女はまず一歩からはじめたい~魔物がいるとか聞いてない!~</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>転生したら第七王子だったので、気ままに魔術を極めます</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>変な家:</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>この音とまれ!</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>新テニスの王子様</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>おじさまと猫</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>侯爵令嬢は手駒を演じる 9(アリアンローズコミックス)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>拾ったものは大切にしましょう 子狼に気に入られた男の転移物語3</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>え、社内システム全てワンオペしている私を解雇ですか?(コミック)5</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>くま クマ 熊 ベアー(コミック)14</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ 通常版</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ふしぎ遊戯 白虎仙記</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>太陽よりも眩しい星</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>社長が私を抱く理由</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>せっかく農家に転生したので勇者は目指しません</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>身代わり令嬢を救ったのは冷酷無慈悲な氷の王子の愛でした1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ブラッドフレンド</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ビッチが異世界に現れたッ!</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>平民出身の帝国将官、無能な貴族上官を蹂躙して成り上がる</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>嘘よみと偽飾の王女</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ねずみの初恋</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>無能と呼ばれた『精霊たらし』~実は異能で、精霊界では伝説的ヒーローでした~@COMIC</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>グラぱらっ!</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sランクパーティから解雇された~『呪いのアイテム』しか作れませんが、その性能はアーティファクト級なり……!~</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>江戸前エルフ</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>経験済みなキミと、経験ゼロなオレが、お付き合いする話。</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>後宮茶妃伝~寵妃は愛より茶が欲しい~</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん if Episode of 魔フィア</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>頼くんとヨリを戻すわけには!</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ミステリと言う勿れ</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>カグラバチ</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>自称悪役令嬢な婚約者の観察記録。</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>義妹生活</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>結液感戦</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>臓腑の花束</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>さよなら僕のメイド様</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>背徳お姉さんの誘惑に君は勝てるか?</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>処刑された死に戻りの第六王子は故国を捨て、隣国のギロチン皇女と復讐を誓う第1話</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>廃嫡貴族のスキルマスター~追放されましたが、『スキル創造』で世界最強になりました!?~@COMIC 第1話</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>竜騎士のお気に入り:</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>イケボ配信者は俺狙い!?</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ゴールデンドロップ</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>暴力万歳</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ブルーピリオド</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>地元のいじめっ子達に仕返ししようとしたら、別の戦いが始まった。</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>きみは世界の中心です</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>妹は知っている</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>最強の職業は勇者でも賢者でもなく鑑定士(仮)らしいですよ?12</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ゴールデン・ガイ</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>鬼の花嫁</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>異世界魔法は遅れてる!13</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>新しいゲーム始めました。@COMIC ~使命もないのに最強です?~</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -42,6 +42,7 @@
     <sheet name="2026-06-10" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-06-17" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-06-24" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="2026-07-01" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39804,6 +39805,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと~猫猫の後宮謎解き手帳~</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>バウンサー</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ドラハチ 電子限定描きおろし特典つき</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>超人X</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>オタクに優しいギャルはいない!?</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>月が導く異世界道中17</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>龍狼伝 王霸立国編</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>カッコウの許嫁</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>スキップ・ビート!</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>骸骨騎士様、只今異世界へお出掛け中ⅩⅤ</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ふたりソロキャンプ</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WORST外伝 ゼットン先生</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>帝乃三姉妹は案外、チョロい。</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COSMOS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>カテナチオ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>盤上のオリオン</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>龍と苺</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>魔入りました!入間くん</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>天牌</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>転生貴族、鑑定スキルで成り上がる ~弱小領地を受け継いだので、優秀な人材を増やしていたら、最強領地になってた~</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>アルテ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>世界に一人、全属性魔法の使い手</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mr.CB</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ダストランド</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>変な家:</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>大正學生愛妻家</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>釣って食べたいギャル澤さん</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>百瀬アキラの初恋破綻中。</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>笑顔のたえない職場です。</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ケンガンオメガ</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>紫雲寺家の子供たち</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ハズレ枠ので最強になった俺がすべてを蹂躙するまで</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>現実主義勇者の王国再建記ⅩⅤ</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>恋せよまやかし天使ども</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>鉄拳チンミLegends</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>七つ屋志のぶの宝石匣</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>レッドブルー</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>虐げられ令嬢、辺境の色ボケ老人の後妻になるはずが、美貌の辺境伯さまに溺愛されるなんて聞いていません!</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>今夜、秘めた恋情が溢れたら~極上社長は傷心秘書を逃がさない~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>外商の仕事に恋は含まれますか</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>王様ランキング</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>失格紋の最強賢者 ~世界最強の賢者が更に強くなるために転生しました~</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>薫る花は凛と咲く</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>界変の魔法使い</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>あかね噺</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>虐げられ令嬢、辺境の色ボケ老人の後妻になるはずが、美貌の辺境伯さまに溺愛されるなんて聞いていません!</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>虐げられ令嬢、辺境の色ボケ老人の後妻になるはずが、美貌の辺境伯さまに溺愛されるなんて聞いていません!</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>余命一年の心読みの令嬢は冷酷非道と噂される皇帝に溺愛される~彼の本音は甘すぎます~</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>最恐辺境伯に拾われました、小鳥(=悪女?)です</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>一夜限りのお相手が溺愛先生へと変貌しました1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>黒妖の花嫁~忌み嫌われた私が冷酷大尉に愛されるまで~1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>イマリさんは旅上戸(コミック) 1話</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>王国の鍵 -Tale of the Missing Princess- 第1話</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>木洩れ日のひと</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LILIーMEN</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>実は私が本物だった</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>WORST外伝 ドクロ</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ニューノーマル9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>空挺ドラゴンズ</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>聖なる乙女と秘めごとを</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ブラック職場を追放された俺、氷の令嬢に拾われる ~生活魔法を駆使して無双していたら、幸せな暮らしが始まりました~</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ヤンキー君と科学ごはん</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>陸奥圓明流異界伝 修羅の紋 ムツさんはチョー強い?!</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ドラハチ</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>多聞くん今どっち!?</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>天使1/2方程式</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>俺の声に堕ちてください</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ウィッチウォッチ</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>余命一年の心読みの令嬢は冷酷非道と噂される皇帝に溺愛される~彼の本音は甘すぎます~</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>余命一年の心読みの令嬢は冷酷非道と噂される皇帝に溺愛される~彼の本音は甘すぎます~</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>最恐辺境伯に拾われました、小鳥(=悪女?)です</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>最恐辺境伯に拾われました、小鳥(=悪女?)です</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>婚約者に嫌われているようなので離れてみたら、なぜか抗議されました</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>いきなり結婚宣言~裏切られ絶望した私に待っていたのは溺愛でした~1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>私の中の怪物~歌姫の復讐~</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>悪役ですが、長生きしたいです(フルカラー)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>家臣に恵まれた転生貴族の幸せな日常</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>図書館の大魔術師</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -43,6 +43,7 @@
     <sheet name="2026-06-17" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-06-24" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-07-01" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="2026-07-08" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41141,6 +41142,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる外伝 竜双剣の軌跡</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>異世界ハーレムループ~繰り返される1日から脱出する為に抱きまくります~</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>魔力0でも魔術狂いだったので、第二の人生では無双する~俺だけ知っている魔術知識で極大魔法をぶっ放す~</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>『廃品回収』スキルで手に入れた訳ありチート魔剣が最強すぎる件~役立たずと捨てられた俺は、異世界のガラクタたちと成り上がる~</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ふたりソロキャンプ</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>自称悪役令嬢な婚約者の観察記録。</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>はじまりの町の育て屋さん~追放された万能育成師はポンコツ冒険者を覚醒させて最強スローライフを目指します~ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>田舎暮らしの魔草薬師は返り咲く~不正はびこる元職場を解雇されたので独立したら、なぜか各界の超一流たちが集まってきました~</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ディストピア~移住先は不貞の島でした~1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>センパイ、自宅警備員の雇用はいかがですか? THE COMIC</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>爆乳たちに追放されたが戻れと言われても、もう遅……戻りましゅぅぅ! THE COMIC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>バウンサー</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ハニーレモンソーダ Another Stories</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>不可抗力のI LOVE YOU</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>うちの弟どもがすみません</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>クラッシュベリー・カルテット</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>モブ高生の俺でも冒険者になればリア充になれますか?(ノヴァコミックス)8</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>「あのとき助けていただいたモンスター娘です。」異世界おっさん教師 突然のモテ期に困惑する</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>魔力0で最強の大賢者 ~それは魔法ではない、物理だ!~:</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>焼いてるふたり</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>異世界でカフェを開店しました。17</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>悪食令嬢と狂血公爵 ~その魔物、私が美味しくいただきます!~</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>フェルマーの料理</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>英霊たちから修行を受け続けた最後の英雄は、やがて最強へと成り上がる 第2話</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>冴えないおっさん、実は最強 第2話</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>木洩れ日のひと</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>今日から使える異世界恋愛マニュアル</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>異世界旅はニワトリスと共に</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>クラスで2番目に可愛い女の子と友だちになった</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>大正學生愛妻家</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>最強陰陽師の異世界転生記~下僕の妖怪どもに比べてモンスターが弱すぎるんだが~(コミック)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>玉川さん 出てました?</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと~猫猫の後宮謎解き手帳~</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>イートインワンダーランド</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>俺に都合が良すぎる街 ~支配者スキルで異世界ハーレム無双~</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>桃の花が散る殺に</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>整形リップ~復讐のひと塗り~</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ちびころ転生者のモフモフ森暮らし 第2話</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>侯爵令嬢アグリ・カルティアは授かったチートスキルでこっそり農業を謳歌する 第2話</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>元最強の剣士は、異世界魔法に憧れる THE COMIC</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>元最強の剣士は、異世界魔法に憧れる THE COMIC</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>二階堂地獄ゴルフ</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>陸上自衛隊特務諜報機関 別班の犬</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>柚木さんちの四兄弟。</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>君を忘れる恋がしたい</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>日本三國</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>木洩れ日のひと</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>人造魔女は人にあらず</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>らぶぶいっ!</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>この恋、一旦持ち帰らせていただきます!</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>異世界旅はニワトリスと共に</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>異世界旅はニワトリスと共に</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>京都下鴨 神様のいそうろう</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>即クビになりたいメイドなのに、冷血皇子に執着されています第1話</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>偽装カノジョなのに帝国の皇太子様からの溺愛が止まりません第1話</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>泣いて謝られても教会には戻りません! 追放された元聖女候補ですが、同じく追放された『剣神』さまと意気投合したので第二の人生を始めてます第1話</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>おためしCOMICユニコーンVol.2</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>魔術師クノンは見えている</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mr.CB</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放された白魔導師、Sランク冒険者に拾われる~この白魔導師が規格外すぎる~(コミック)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ガチャを回して仲間を増やす 最強の美少女軍団を作り上げろ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>龍とカメレオン</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>隣の元カレくん 単行本版</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>この音とまれ!</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>俺の声に堕ちてください</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>直径3cmの召喚陣&lt;リミットリング&gt;で「雑魚すら呼べない」と蔑まれた底辺召喚士が頂点に立つまで1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>となりの響くん</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>イートインワンダーランド</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>イートインワンダーランド</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>はるい駈歩</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>桃の花が散る殺に</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>桃の花が散る殺に</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>六畳間のカミの国</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>妹が「いらない」と捨てた伯爵様と結婚したのに、今更返せと言われても困ります第1話</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>目が覚めました 奪われた婚約者はきっぱりと捨てました第1話</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>役目を果たした日陰の勇者は、辺境で自由に生きていきます</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>英霊たちから修行を受け続けた最後の英雄は、やがて最強へと成り上がる 第3話</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>冴えないおっさん、実は最強 第3話</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ガチャを回して仲間を増やす 最強の美少女軍団を作り上げろ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>アイヲンモール異世界店、本日グランドオープン! THE COMIC</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件~魔物の国の歩き方~</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -44,6 +44,7 @@
     <sheet name="2026-06-24" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-07-01" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-07-08" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="2026-07-15" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42478,6 +42479,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>魔男のイチ</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER カラー版</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>フェルマーの料理</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ダークギャザリング</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>血界戦線 Beat 3 Peat</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>キン肉マン</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ラーメン赤猫</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>オーイ! とんぼ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>チェンソーマン</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ダーウィン事変</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ケントゥリア</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ザ・シェフ(新装SP版)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>呪われ公爵と捨てられた花嫁の最愛婚1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>秘密 season</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ふつうの軽音部</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ありす、宇宙までも</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ONE PIECE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ザ・シェフ(新装SP版)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ザ・シェフ(新装SP版)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ザ・シェフ(新装SP版)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ザ・シェフ(新装SP版)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>団長改め狂犬騎士のしつけ役</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>落第賢者の学院無双 ~二度目の転生、Sランクチート魔術師冒険録~</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ダンダダン</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>はじまりの町の育て屋さん~追放された万能育成師はポンコツ冒険者を覚醒させて最強スローライフを目指します~ THE COMIC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ザ・シェフ 大合本版</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>人質として売られた夜の聖女は隣国の大公様に嫁ぐ1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>『廃品回収』スキルで手に入れた訳ありチート魔剣が最強すぎる件~役立たずと捨てられた俺は、異世界のガラクタたちと成り上がる~</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>神血の救世主~0.00000001%を引き当て最強へ~</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>技巧貸与&lt;スキル・レンダー&gt;のとりかえし~トイチって最初に言ったよな?~</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>昴と彗星</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ひまてん!</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>どきどきDO!れみ</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ザ・シェフ 大合本版</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件~魔物の国の歩き方~</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ディストピア~移住先は不貞の島でした~1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>鉄鍋のジャン!!2nd</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>団長改め狂犬騎士のしつけ役</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>団長改め狂犬騎士のしつけ役</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>パニくる!? パニック障害、「焦らない!」が効くクスリ。</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>友だち以上恋人未満の魔法使いたち1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>公爵様、悪妻の私はもう放っておいてください:</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>最強陰陽師の異世界転生記~下僕の妖怪どもに比べてモンスターが弱すぎるんだが~(コミック)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>悪食令嬢と狂血公爵 ~その魔物、私が美味しくいただきます!~</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>薬屋のひとりごと~猫猫の後宮謎解き手帳~</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>マリッジトキシン</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BORUTO-ボルト- -TWO BLUE VORTEX-</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>結婚よそうよ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ボーイズ・メイクアップ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ハローエミリ</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ゾンビが銀座にやって来る</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>スペシャルミルクティ</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>爆乳たちに追放されたが戻れと言われても、もう遅……戻りましゅぅぅ! THE COMIC</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>田舎暮らしの魔草薬師は返り咲く~不正はびこる元職場を解雇されたので独立したら、なぜか各界の超一流たちが集まってきました~</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>異世界ハーレムループ~繰り返される1日から脱出する為に抱きまくります~</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>折り紙職人ミモザの日記帳1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>全滅エンドを死に物狂いで回避した。パーティが病んだ。</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>新米魔女の異世界お気楽旅 ~異世界に落ちた元アラフォー社畜は魔女の弟子を名乗り第二の人生を謳歌する~</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>図書館の大魔術師</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>俺だけ最強超越者~全世界のチート師匠に認められた~</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>バウンサー</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>俺んちに来た女騎士と田舎暮らしすることになった件</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>勇者パーティーを追放された白魔導師、Sランク冒険者に拾われる~この白魔導師が規格外すぎる~(コミック)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>空挺ドラゴンズ</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>復讐の同窓会</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ホタルの嫁入り</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>無自覚な天才少女は気付かない</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>そうだ、売国しよう~天才王子の赤字国家再生術~</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>永世乙女の戦い方</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>マリッジシンデレラ 拾われた花嫁は一途な副社長に溺愛される</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Forward!-フォワード!- 世界一のサッカー選手に憑依されたので、とりあえずサッカーやってみる。</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>センパイ、自宅警備員の雇用はいかがですか? THE COMIC</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SPY×FAMILY</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>彼女、お借りします</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/weekly_ranking.xlsx
+++ b/weekly_ranking.xlsx
@@ -45,6 +45,7 @@
     <sheet name="2026-07-01" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-07-08" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-07-15" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="2026-07-22" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43815,6 +43816,1342 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>黄泉のツガイ</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ザ・ファブル The third secret</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>弱虫ペダル</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ヘルモード ~やり込み好きのゲーマーは廃設定の異世界で無双する~はじまりの召喚士14</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>刃牙らへん</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>しょせん他人事ですから ~とある弁護士の本音の仕事~</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>桃源暗鬼</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>味方が弱すぎて補助魔法に徹していた宮廷魔法師、追放されて最強を目指す</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>出会って5秒でバトル</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>暗殺者である俺のステータスが勇者よりも明らかに強いのだが</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>領民0人スタートの辺境領主様 ~青のディアスと蒼角の乙女~15</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>老後に備えて異世界で8万枚の金貨を貯めます</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>落第賢者の学院無双 ~二度目の転生、Sランクチート魔術師冒険録~</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>リィンカーネーションの花弁</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>100万の命の上に俺は立っている</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>アマチュアビジランテ</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>辺境の薬師、都でSランク冒険者となる~英雄村の少年がチート薬で無自覚無双~</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>29歳独身中堅冒険者の日常</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>金色のガッシュ!! 2 Page</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>デキる猫は今日も憂鬱</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>劣等人の魔剣使い スキルボードを駆使して最強に至る</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>俺だけレベルアップな件</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BLUE GIANT MOMENTUM</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ブルーロック</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>結婚しましょう、恋する前に</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>組長娘と世話係</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>史上最強オークさんの楽しい異世界ハーレムづくり</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>片田舎のおっさん、剣聖になる~ただの田舎の剣術師範だったのに、大成した弟子たちが俺を放ってくれない件~</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ドローイング 最強漫画家はお絵描きスキルで異世界無双する!19</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>だれでも抱けるキミが好き</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>最強で最速の無限レベルアップ ~スキルとでレベル上限の枷が外れた俺は無双する~</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ポーション頼みで生き延びます! 続</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ここは俺に任せて先に行けと言ってから10年がたったら伝説になっていた。</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>花野井くんと恋の病</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>きみの横顔を見ていた</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JJM 女子柔道部物語 社会人編</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>転生したらスライムだった件</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>落ちこぼれだった兄が実は最強 ~史上最強の勇者は転生し、学園で無自覚に無双する~</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>最弱貴族に転生したので悪役たちを集めてみた</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>限界集落を脱村した錬金術士、都会で“最強”なのがバレまくる。~老害どもにはいい加減愛想が尽きました~</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>サイコアイズ</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>育成スキルはもういらないと勇者パーティを解雇されたので、退職金がわりにもらったを強くしてみる</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>アオアシ ブラザーフット</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>星降る王国のニナ</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>アオのハコ</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>これ描いて死ね</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ゲーム中盤で死ぬ悪役貴族に転生したので、外れスキルを駆使して最強を目指してみた</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>魔法医レクスの変態カルテ</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>そうだ、売国しよう~天才王子の赤字国家再生術~</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>となりの席のヤツがそういう目で見てくる</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>血界戦線 Beat 3 Peat</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>鬼の軍人と稀血の花嫁</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>かりそめ婚~この溺愛は契約にありません~</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>フェルマーの料理</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>最弱な僕は&lt;壁抜けバグ&gt;で成り上がる~壁をすり抜けたら、初回クリア報酬を無限回収できました!~</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ブーツレグ</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>はめつのおうこく</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>田んぼで拾った女騎士、田舎で俺の嫁だと思われている</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>追放された転生重騎士はゲーム知識で無双する</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER カラー版</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HUNTER×HUNTER</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>キャプテン翼</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
